--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-10T12:47:01.447Z</t>
+    <t>2026-06-10T13:58:28.977Z</t>
   </si>
   <si>
     <t>REXULTI® (brexpiprazole) | Patient Information Website</t>
